--- a/output/pdf_financials_xlsx/KETA.xlsx
+++ b/output/pdf_financials_xlsx/KETA.xlsx
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.037015</v>
+        <v>0.318838</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.009606</v>
       </c>
     </row>
     <row r="11">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.02304</v>
+        <v>-0.304863</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002825</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001196</v>
       </c>
     </row>
     <row r="35">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002825</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001196</v>
       </c>
     </row>
     <row r="37">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
